--- a/data/info_for_pdf.xlsx
+++ b/data/info_for_pdf.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelmolenaar/Desktop/BROGAARD/Gaard/Gaard Reporting System/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BF861B-7D05-714F-8514-17E2571A53AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCEEB53-3A64-384F-B74D-D11A51EAA272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" xr2:uid="{6D522E3E-A00D-E248-87E0-EF62B3A29ADA}"/>
   </bookViews>

--- a/data/info_for_pdf.xlsx
+++ b/data/info_for_pdf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelmolenaar/Desktop/BROGAARD/Gaard/Gaard Reporting System/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCEEB53-3A64-384F-B74D-D11A51EAA272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC1901A-5554-B449-8370-69B433AA6C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" xr2:uid="{6D522E3E-A00D-E248-87E0-EF62B3A29ADA}"/>
   </bookViews>
@@ -196,7 +196,7 @@
     <t>quarter</t>
   </si>
   <si>
-    <t>Q4</t>
+    <t>Q1</t>
   </si>
 </sst>
 </file>
@@ -628,7 +628,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="1">
-        <v>46050</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">

--- a/data/info_for_pdf.xlsx
+++ b/data/info_for_pdf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelmolenaar/Desktop/BROGAARD/Gaard/Gaard Reporting System/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC1901A-5554-B449-8370-69B433AA6C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F379EEE5-EEB1-2A43-A520-658BA23CB9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" xr2:uid="{6D522E3E-A00D-E248-87E0-EF62B3A29ADA}"/>
+    <workbookView xWindow="7320" yWindow="780" windowWidth="33800" windowHeight="25800" xr2:uid="{6D522E3E-A00D-E248-87E0-EF62B3A29ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="47">
   <si>
     <t>key</t>
   </si>
@@ -77,45 +77,6 @@
     <t>page_4_ips_us_equity_target</t>
   </si>
   <si>
-    <t>page_4_ips_non_us_equity_dev_range_min</t>
-  </si>
-  <si>
-    <t>page_4_ips_non_us_equity_dev_range_max</t>
-  </si>
-  <si>
-    <t>page_4_ips_non_us_equity_dev_target</t>
-  </si>
-  <si>
-    <t>page_4_ips_non_us_equity_em_range_min</t>
-  </si>
-  <si>
-    <t>page_4_ips_non_us_equity_em_range_max</t>
-  </si>
-  <si>
-    <t>page_4_ips_non_us_equity_em_target</t>
-  </si>
-  <si>
-    <t>page_4_ips_non_us_fixed_income_global_range_min</t>
-  </si>
-  <si>
-    <t>page_4_ips_non_us_fixed_income_global_range_max</t>
-  </si>
-  <si>
-    <t>page_4_ips_non_us_fixed_income_global_target</t>
-  </si>
-  <si>
-    <t>page_4_ips_us_fixed_income_range_min</t>
-  </si>
-  <si>
-    <t>page_4_ips_us_fixed_income_range_max</t>
-  </si>
-  <si>
-    <t>page_4_ips_us_fixed_income_target</t>
-  </si>
-  <si>
-    <t>page_4_ips_total_fixed_income_target</t>
-  </si>
-  <si>
     <t>page_4_ips_alternatives_range_min</t>
   </si>
   <si>
@@ -152,21 +113,6 @@
     <t>page_4_us_equity_current</t>
   </si>
   <si>
-    <t>page_4_non_us_equity_dev_current</t>
-  </si>
-  <si>
-    <t>page_4_non_us_equity_em_current</t>
-  </si>
-  <si>
-    <t>page_4_non_us_fixed_income_global_current</t>
-  </si>
-  <si>
-    <t>page_4_us_fixed_income_current</t>
-  </si>
-  <si>
-    <t>page_4_total_fixed_income_current</t>
-  </si>
-  <si>
     <t>page_4_alternatives_current</t>
   </si>
   <si>
@@ -182,21 +128,59 @@
     <t>Gaard Capital LLC</t>
   </si>
   <si>
-    <t>Treasury yields moved lower again in March even as the Federal Reserve held its policy rate steady for the second consecutive FOMC meeting. The dominant theme of the quarter was uncertainty surrounding President Trump’s tariff policy, characterized by rapidly changing announcements and reversals. On March 3, a 25% tariff was imposed on imports from Mexico and Canada, along with an additional 10% tariff on Chinese goods. Within days, exemptions were granted for USMCA-covered goods, while new tariffs were announced on Canadian dairy and lumber, followed by a 25% levy on all imported steel and aluminum. Retaliation from trade partners was swift, and several countries sought new trade agreements among themselves, increasing global trade fragmentation.
-Markets reacted negatively to this uncertainty. Stocks were highly volatile, and the S&amp;P 500 fell nearly 6% in March despite record corporate profits in the prior quarter. Investor concerns shifted from tariff-driven inflation to fears of an economic slowdown or recession, as heightened uncertainty likely weighed on business investment and consumer spending.
-Hard economic data still reflected pre-tariff conditions and therefore provided limited insight into future activity. Employment remained solid, with February nonfarm payrolls rising 151,000 and the unemployment rate edging up to 4.1%, still near historic lows. Inflation eased modestly: both headline and core CPI rose 0.2% in February, below expectations, with year-over-year headline inflation falling to 2.8% and core CPI to 3.1%, a four-year low. Grocery prices were flat and gasoline prices declined slightly.
-Consumer spending showed clear weakness. February retail sales rose only 0.2%, well below forecasts, while January sales were revised down to a 1.2% decline. Spending fell in 7 of 13 categories. Softer survey data reflected growing concern: the Conference Board consumer confidence index dropped sharply in March, and expectations fell to a 12-year low consistent with recessionary conditions. Inflation expectations rose, a trend reinforced by the University of Michigan sentiment survey, which showed long-term inflation expectations at a three-decade high.
-At its March meeting, the Federal Reserve left rates unchanged and revised projections to show slightly higher inflation and lower 2025 GDP growth. The dot plot still signaled two rate cuts in 2025, though with reduced confidence. Chair Powell emphasized that tariff-driven inflation would likely be temporary, suggesting policymakers could ease policy if economic or labor market conditions deteriorated.
-While a near-term recession remains uncertain, the Atlanta Fed GDPNow estimate pointed to a sharp Q1 contraction of -3.7% as of April 1. Although this estimate may improve with additional data, it underscores a sudden slowdown. With few positive catalysts expected in the second quarter and trade tensions still elevated, financial markets appear increasingly positioned for slower growth and lower interest rates.</t>
-  </si>
-  <si>
-    <t>The purpose of the endowment is to generate income and long-term appreciation that will be expended according to donor- or Board-approved purposes and spending policy for each endowment. The goal of the Organization’s investment program is to achieve a 5% nominal total return, net of all management and custodial fees. This target represents the long-term performance needed to support the Organization’s mission by funding annual spending requirements, covering inflation, and maintaining the purchasing power of invested assets.</t>
-  </si>
-  <si>
     <t>quarter</t>
   </si>
   <si>
     <t>Q1</t>
+  </si>
+  <si>
+    <t>The purpose of the portfolio is to preserve capital while generating moderate income and long-term appreciation. The investment strategy is designed to balance stability with growth, maintaining a diversified allocation across asset classes. The purpose is to achieve an average annual nominal total return of 6%, net of all management and custodial fees, over a full market cycle. The target reflects a moderate risk profile, emphasizing downside protection, income generation, and the preservation of purchasing power over time, while still participating in market growth.</t>
+  </si>
+  <si>
+    <t>account</t>
+  </si>
+  <si>
+    <t>Brogaard</t>
+  </si>
+  <si>
+    <t>page_4_ips_non_us_equity_range_min</t>
+  </si>
+  <si>
+    <t>page_4_ips_non_us_equity_range_max</t>
+  </si>
+  <si>
+    <t>page_4_ips_non_us_equity_target</t>
+  </si>
+  <si>
+    <t>page_4_non_us_equity_current</t>
+  </si>
+  <si>
+    <t>page_4_ips_fixed_income_range_min</t>
+  </si>
+  <si>
+    <t>page_4_ips_fixed_income_range_max</t>
+  </si>
+  <si>
+    <t>page_4_ips_fixed_income_target</t>
+  </si>
+  <si>
+    <t>page_4_fixed_income_current</t>
+  </si>
+  <si>
+    <t>Paula C Hurley</t>
+  </si>
+  <si>
+    <t>John P Mattox</t>
+  </si>
+  <si>
+    <t>The purpose of the portfolio is to achieve long-term capital appreciation while accepting a higher degree of short-term volatility in pursuit of growth. The investment strategy is designed to maximize equity exposure within a diversified framework. The objective is to achieve an average annual nominal total return of 7%, net of all management and custodial fees, over a full market cycle. This target reflects a growth-oriented risk profile, prioritizing capital appreciation and long-term wealth accumulation, while maintaining sufficient diversification to manage risk over time.</t>
+  </si>
+  <si>
+    <t>The first quarter of 2026 was a turning point. After a strong 2025, investors rotated from expensive U.S. mega-cap tech toward value, smaller caps, and international stocks as AI valuation concerns weighed on the largest growth names. That rotation held through much of January and into February until the Middle East conflict began in late February, sending oil prices surging nearly 80 percent for the quarter and raising geopolitical risk.
+Equities weakened sharply in March. The S&amp;P 500 fell 4.5 percent for the quarter, its worst performance since 2022, with the sharpest drawdowns in the Magnificent Seven while value, energy, international, and small and micro caps held up better and market leadership continued to broaden away from U.S. large-cap growth. Energy also posted the strongest gains of any sector on both a trailing one-year and one-month basis, which highlighted how quickly relative strength can migrate when an energy shock hits a crowded growth trade.
+Commodities led, with oil up nearly 80 percent, broader commodity indices up approximately 40 percent, and strong returns in gold and silver despite mid-quarter volatility.
+Growth disappointed as Q4 2025 GDP printed at 0.5 percent, well below the 3 percent forecast, though full-year 2026 projections were revised to 2.5 percent, suggesting the underlying trajectory remained intact. Inflation reaccelerated, with core CPI at 2.6 percent in March above the Fed’s 2 percent target and headline CPI at 3.3 percent on the energy shock, alongside tariff pressures at their highest effective rate since the 1940s, which together removed the near-term case for cuts. The Fed held rates steady at both Q1 meetings and 17 of 19 FOMC participants flagged upside inflation risks in March, shifting market focus toward possible hikes by year end.
+The unemployment rate stayed at 4.3 percent, goods spending softened as services held steadier, and sentiment weakened through March. Fixed income posted negative returns across major sectors as stocks and bonds fell together, the stock-bond correlation rose, and Treasuries led global bonds on a relative basis with corporate spreads wider but still below recessionary levels. With the VIX peaking above 30 in late March, volatility may stay elevated as markets digest higher inflation and policy uncertainty, and broad diversification across asset classes, geographies, and styles remains a sensible posture for Q2.</t>
   </si>
 </sst>
 </file>
@@ -227,7 +211,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -235,14 +219,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,45 +585,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B2519F-DAD7-424B-BCCD-A6F236E5C7A3}">
-  <dimension ref="B3:C57"/>
+  <dimension ref="B3:D90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="51.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="D3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -623,15 +635,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -639,276 +651,736 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
         <v>10</v>
       </c>
-      <c r="C15">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
+      <c r="C18" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C16">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
+      <c r="C22" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C17">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
+      <c r="C26" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B35" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B39" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
         <v>37</v>
       </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="C40" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B49" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="D52" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="D56" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.65</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
         <v>13</v>
       </c>
-      <c r="C20">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="C60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="3">
+        <v>0</v>
+      </c>
+      <c r="D61" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="3">
+        <v>0</v>
+      </c>
+      <c r="D62" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>0</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
         <v>14</v>
       </c>
-      <c r="C21">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+      <c r="C64" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D65" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D66" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B67" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
         <v>15</v>
       </c>
-      <c r="C22">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+      <c r="C68" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
         <v>16</v>
       </c>
-      <c r="C25">
+      <c r="C74" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+    <row r="75" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="3">
+        <v>0</v>
+      </c>
+      <c r="D75" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="3">
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B77" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="7">
+        <v>0</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
         <v>17</v>
       </c>
-      <c r="C26">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+      <c r="C78" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D79" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D80" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B81" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
         <v>18</v>
       </c>
-      <c r="C27">
+      <c r="C82">
         <v>0.05</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    <row r="83" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83">
+        <v>0.05</v>
+      </c>
+      <c r="D83" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84">
+        <v>0.05</v>
+      </c>
+      <c r="D84" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B85" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B88" t="s">
         <v>19</v>
       </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+      <c r="C88" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B90" t="s">
         <v>20</v>
       </c>
-      <c r="C31">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+      <c r="C90" t="s">
         <v>21</v>
-      </c>
-      <c r="C32">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>25</v>
-      </c>
-      <c r="C42">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>26</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>28</v>
-      </c>
-      <c r="C47">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
